--- a/file_upload_forms/013_custom_heat_transfer_patch_order_form--file_upload_forms.xlsx
+++ b/file_upload_forms/013_custom_heat_transfer_patch_order_form--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,69 +515,69 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_1</t>
+          <t>heat_transfer_patch_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Custom Heat Transfer Patch Orders</t>
+          <t>What type of heat transfer patch do you need?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_2</t>
+          <t>heat_transfer_patch_size</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>How many heat transfer patches do you need?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_3</t>
+          <t>heat_transfer_patch_location_source</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>What is the location of the heat source?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,41 +589,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_4</t>
+          <t>heat_transfer_patch_location_sink</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>What is the location of the heat sink?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_5</t>
+          <t>heat_transfer_medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>What type of medium do you use for heat transfer?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_6</t>
+          <t>heat_transfer_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Date and time of heat transfer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,41 +658,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_7</t>
+          <t>heat_transfer_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Time of heat transfer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_8</t>
+          <t>heat_transfer_additional_comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Enter any additional comments or notes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_9</t>
+          <t>heat_transfer_patch_select_multiple_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Select multiple options</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_10</t>
+          <t>heat_transfer_patch_description</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Enter a brief description of the heat transfer patch</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_11</t>
+          <t>heat_transfer_client_email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Enter the email address of the client</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,110 +773,110 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_12</t>
+          <t>heat_transfer_patch_size_description</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Enter a description of the patch size</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_13</t>
+          <t>heat_transfer_patch_select_multiple_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Heat Transfer Patch Select Multiple 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_14</t>
+          <t>heat_transfer_patch_note_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Enter a note</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_15</t>
+          <t>heat_transfer_patch_note_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Enter another note</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_16</t>
+          <t>heat_transfer_patch_note_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Heat Transfer Patch Note 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,64 +888,64 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_17</t>
+          <t>heat_transfer_patch_size_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Enter another patch size</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_18</t>
+          <t>heat_transfer_patch_select_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Select one option</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_19</t>
+          <t>heat_transfer_patch_select_multiple_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Heat Transfer Patch Select Multiple 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -957,64 +957,64 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_20</t>
+          <t>heat_transfer_patch_select_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Heat Transfer Patch Select 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_21</t>
+          <t>heat_transfer_patch_date</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Enter a date</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_22</t>
+          <t>heat_transfer_patch_time</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Enter a time</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1026,18 +1026,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_23</t>
+          <t>heat_transfer_patch_size_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Heat Transfer Patch Size 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1049,41 +1049,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_24</t>
+          <t>heat_transfer_patch_size_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Heat Transfer Patch Size 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_25</t>
+          <t>heat_transfer_patch_size_5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Heat Transfer Patches</t>
+          <t>Heat Transfer Patch Size 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,340 +1126,289 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_2_choices</t>
+          <t>heat_transfer_patch_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option_1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_2_choices</t>
+          <t>heat_transfer_patch_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option_2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_3_choices</t>
+          <t>heat_transfer_medium_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option_1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_3_choices</t>
+          <t>heat_transfer_medium_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option_2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_3_choices</t>
+          <t>heat_transfer_patch_select_multiple_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option_3'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'option_3'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_8_choices</t>
+          <t>heat_transfer_patch_select_multiple_1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option_1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_8_choices</t>
+          <t>heat_transfer_patch_select_multiple_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option_2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_9_choices</t>
+          <t>heat_transfer_patch_select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option_1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_9_choices</t>
+          <t>heat_transfer_patch_select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option_2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_9_choices</t>
+          <t>heat_transfer_patch_select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'option_3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_15_choices</t>
+          <t>heat_transfer_patch_select_1_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option_1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_15_choices</t>
+          <t>heat_transfer_patch_select_1_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option_2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_16_choices</t>
+          <t>heat_transfer_patch_select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option_1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_16_choices</t>
+          <t>heat_transfer_patch_select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option_2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_20_choices</t>
+          <t>heat_transfer_patch_select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option_1'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_20_choices</t>
+          <t>heat_transfer_patch_select_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option_2'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option_2'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>custom_heat_transfer_patch_order_form_page_21_choices</t>
+          <t>heat_transfer_patch_select_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option_1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>custom_heat_transfer_patch_order_form_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'label':_'option_2',_'value':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 2', 'value': 'option_2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>custom_heat_transfer_patch_order_form_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'label':_'option_1',_'value':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 1', 'value': 'option_1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>custom_heat_transfer_patch_order_form_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'label':_'option_2',_'value':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 2', 'value': 'option_2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
